--- a/Extra/TestCase.xlsx
+++ b/Extra/TestCase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenminhphu/Desktop/Đại Học/Kỳ 4/Lập Trình Mạng/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenminhphu/Documents/DEV/LTM/GR12---LTMang/Extra/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B0B642-B9D2-A048-8301-216EAA02298D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93B24F24-50F9-A24F-8C5A-9F2EBB41095D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8780" yWindow="500" windowWidth="24820" windowHeight="20500" xr2:uid="{98CF65A9-BED2-B54A-93D9-E7FC4BDEF8E6}"/>
+    <workbookView xWindow="80" yWindow="500" windowWidth="33520" windowHeight="20500" xr2:uid="{98CF65A9-BED2-B54A-93D9-E7FC4BDEF8E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="165">
   <si>
     <t>No.</t>
   </si>
@@ -524,13 +524,61 @@
   </si>
   <si>
     <t>Input</t>
+  </si>
+  <si>
+    <t>Nhóm:</t>
+  </si>
+  <si>
+    <t>Minh Phú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phiên bản: </t>
+  </si>
+  <si>
+    <t>Ngày test:</t>
+  </si>
+  <si>
+    <t>Người thực hiện:</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Client B vẫn hoạt động bình thường trong sever, không bị crash out</t>
+  </si>
+  <si>
+    <t>Màn hình terminal in ra: "CHAT SERVER TCP ĐÃ KHỞI CHẠY TẠI PORT 5000"</t>
+  </si>
+  <si>
+    <t>Cả 3 clients đều được kết nối với nhau, nhận và gửi được tin nhắn</t>
+  </si>
+  <si>
+    <t>Màn hình terminal của server hiển thị nội dung mà client gửi</t>
+  </si>
+  <si>
+    <t>Màn hình UI của client chỉ hiển thị tin nhắn mà người dùng gửi</t>
+  </si>
+  <si>
+    <t>Clients kết nối thành công ở port 5000</t>
+  </si>
+  <si>
+    <t>thông báo pop-up hiện lên dòng thông báo " Không kết nối được server, hãy đảm bảo server đã được chạy thành công"</t>
+  </si>
+  <si>
+    <t>Uncheck</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -562,8 +610,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -589,18 +644,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF3FB"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -610,8 +654,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -635,15 +703,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -661,9 +720,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -675,102 +732,137 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFAAAAAA"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FFAAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFAAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFAAAAAA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFAAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFAAAAAA"/>
-      </right>
+      <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFAAAAAA"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1086,873 +1178,1028 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE567999-79F1-3945-926E-7804499D8BB2}">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15" style="6" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="33" style="6" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="38.1640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="43.83203125" style="6" customWidth="1"/>
-    <col min="7" max="10" width="14.83203125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="8"/>
+    <col min="1" max="1" width="15" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="33" style="4" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="38.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="43.83203125" style="4" customWidth="1"/>
+    <col min="7" max="10" width="14.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="4">
+        <v>12</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E5" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F5" s="16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="G5" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="6" t="s">
+      <c r="F6" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="27"/>
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
-      <c r="B14" s="6" t="s">
+      <c r="F7" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="27"/>
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="27"/>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="27"/>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="27"/>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="27"/>
+      <c r="B14" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:10" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="13"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="13"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="23"/>
+      <c r="G19" s="24" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:10" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="27"/>
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="24" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="13"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="24" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" s="13"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="23"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
-      <c r="B25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="13"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="13"/>
+      <c r="A26" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
-      <c r="B27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="13"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15"/>
-      <c r="B28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="13"/>
+      <c r="A28" s="27"/>
+      <c r="B28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="23"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="11"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:10" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
+      <c r="A30" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="23"/>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="28"/>
+      <c r="B31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" s="23"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" s="13"/>
-    </row>
-    <row r="33" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="13"/>
-    </row>
-    <row r="34" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
-      <c r="B34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-    </row>
-    <row r="36" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="13"/>
-    </row>
-    <row r="37" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="16"/>
-      <c r="B37" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F37" s="13"/>
-    </row>
-    <row r="38" spans="1:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="16"/>
-      <c r="B38" s="6" t="s">
+      <c r="A32" s="28"/>
+      <c r="B32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C32" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D32" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E32" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="1:10" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="12"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="28"/>
+      <c r="B35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="28"/>
+      <c r="B36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" s="22" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" s="23"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="27"/>
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="23"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F40" s="13"/>
-    </row>
-    <row r="41" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="16"/>
-      <c r="B41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F41" s="13"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="23"/>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" s="22" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
     </row>
     <row r="42" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="16"/>
-      <c r="B42" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F42" s="13"/>
-    </row>
-    <row r="43" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="A42" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="28"/>
+      <c r="B43" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" s="23"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F44" s="13"/>
-    </row>
-    <row r="45" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="13"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F44" s="23"/>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" s="22" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
     </row>
     <row r="46" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="15"/>
-      <c r="B46" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F46" s="13"/>
+      <c r="A46" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" s="23"/>
+      <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
+      <c r="A47" s="28"/>
+      <c r="C47" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" s="23"/>
+      <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F48" s="13"/>
-    </row>
-    <row r="49" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="16"/>
-      <c r="B49" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F49" s="13"/>
-    </row>
-    <row r="50" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="16"/>
-      <c r="B50" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F50" s="13"/>
-    </row>
-    <row r="51" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-    </row>
-    <row r="52" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="A48" s="28"/>
+      <c r="C48" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F52" s="13"/>
-    </row>
-    <row r="53" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="16"/>
-      <c r="C53" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="13"/>
-    </row>
-    <row r="54" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="16"/>
-      <c r="C54" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F54" s="13"/>
-    </row>
-    <row r="55" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-    </row>
-    <row r="56" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-    </row>
-    <row r="57" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-    </row>
-    <row r="58" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-    </row>
-    <row r="59" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="3:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="3:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="3:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="3:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="3:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+    </row>
+    <row r="58" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+    </row>
+    <row r="59" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+    </row>
+    <row r="60" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+    </row>
+    <row r="62" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+    </row>
+    <row r="64" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
     </row>
     <row r="65" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
     </row>
     <row r="66" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
     </row>
     <row r="68" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
     </row>
     <row r="69" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
     </row>
     <row r="70" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
     </row>
     <row r="71" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
     </row>
     <row r="72" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
     </row>
     <row r="73" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
     </row>
     <row r="74" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
     </row>
     <row r="75" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
     </row>
     <row r="76" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-    </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-    </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-    </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-    </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-    </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-    </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:A16"/>
+  <mergeCells count="14">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A34:A36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G41" xr:uid="{DFED51B3-DB0D-B443-894B-15EE2FC3F319}">
+      <formula1>$J$6:$J$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:G10 G12:G14 G16:G24 G26:G32 G34:G36 G38:G40 G42:G44 G46:G48" xr:uid="{CBF4EDF2-B8BD-E74A-9D02-8074D2166944}">
+      <formula1>$I$6:$I$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>